--- a/data/performance/daily/signal_list_2026-06-10.xlsx
+++ b/data/performance/daily/signal_list_2026-06-10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-10.xlsx
+++ b/data/performance/daily/signal_list_2026-06-10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-06-10.xlsx
+++ b/data/performance/daily/signal_list_2026-06-10.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,12 +663,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-6.39</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -753,7 +784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -763,9 +794,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -795,7 +827,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -820,15 +852,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -865,12 +902,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -902,17 +944,22 @@
       <c r="G6" s="4" t="n">
         <v>-12.2</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -949,12 +996,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -991,12 +1043,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1028,17 +1085,22 @@
       <c r="G9" s="4" t="n">
         <v>-10.42</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1075,12 +1137,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1112,17 +1179,22 @@
       <c r="G11" s="4" t="n">
         <v>-7.33</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1159,12 +1231,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1196,17 +1273,22 @@
       <c r="G13" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1238,17 +1320,22 @@
       <c r="G14" s="4" t="n">
         <v>-2.84</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1285,12 +1372,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1327,12 +1419,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1369,12 +1466,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1411,12 +1513,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1453,12 +1560,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1490,17 +1602,22 @@
       <c r="G20" s="4" t="n">
         <v>-6.39</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-06-10.xlsx
+++ b/data/performance/daily/signal_list_2026-06-10.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>129</v>
       </c>
       <c r="D5" t="n">
+        <v>130</v>
+      </c>
+      <c r="E5" t="n">
         <v>143</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>158</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>22.48</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>10.85</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>8325</v>
       </c>
       <c r="D6" t="n">
+        <v>8300</v>
+      </c>
+      <c r="E6" t="n">
         <v>8200</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>8350</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>560</v>
       </c>
       <c r="D7" t="n">
+        <v>560</v>
+      </c>
+      <c r="E7" t="n">
         <v>580</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>600</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>3.57</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>106</v>
       </c>
       <c r="D8" t="n">
+        <v>106</v>
+      </c>
+      <c r="E8" t="n">
         <v>105</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>110</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>3.77</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.9399999999999999</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>1095</v>
       </c>
       <c r="D9" t="n">
+        <v>1175</v>
+      </c>
+      <c r="E9" t="n">
         <v>1025</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1210</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-6.39</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -784,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -792,12 +813,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,45 +849,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -886,33 +913,36 @@
         <v>720</v>
       </c>
       <c r="D5" t="n">
+        <v>720</v>
+      </c>
+      <c r="E5" t="n">
         <v>690</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>720</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-4.17</v>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -933,33 +963,36 @@
         <v>6350</v>
       </c>
       <c r="D6" t="n">
+        <v>6375</v>
+      </c>
+      <c r="E6" t="n">
         <v>5575</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>6400</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-12.2</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -983,30 +1016,33 @@
         <v>254</v>
       </c>
       <c r="E7" t="n">
+        <v>254</v>
+      </c>
+      <c r="F7" t="n">
         <v>264</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>4.76</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>0.79</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1032,28 +1068,31 @@
       <c r="E8" t="n">
         <v>3070</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>24.8</v>
+      <c r="F8" t="n">
+        <v>3070</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H8" s="4" t="n">
+        <v>24.8</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1074,33 +1113,36 @@
         <v>24000</v>
       </c>
       <c r="D9" t="n">
+        <v>24050</v>
+      </c>
+      <c r="E9" t="n">
         <v>21500</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>24050</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.21</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-10.42</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1121,33 +1163,36 @@
         <v>270</v>
       </c>
       <c r="D10" t="n">
+        <v>270</v>
+      </c>
+      <c r="E10" t="n">
         <v>254</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>270</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-5.93</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1168,33 +1213,36 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
+        <v>188</v>
+      </c>
+      <c r="E11" t="n">
         <v>177</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>194</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>1.57</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-7.33</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1215,33 +1263,36 @@
         <v>164</v>
       </c>
       <c r="D12" t="n">
+        <v>164</v>
+      </c>
+      <c r="E12" t="n">
         <v>165</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>170</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>3.66</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>0.61</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1262,33 +1313,36 @@
         <v>8325</v>
       </c>
       <c r="D13" t="n">
+        <v>8300</v>
+      </c>
+      <c r="E13" t="n">
         <v>8200</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>8350</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>0.3</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1309,33 +1363,36 @@
         <v>1585</v>
       </c>
       <c r="D14" t="n">
+        <v>1645</v>
+      </c>
+      <c r="E14" t="n">
         <v>1540</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1645</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>3.79</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-2.84</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,33 +1413,36 @@
         <v>560</v>
       </c>
       <c r="D15" t="n">
+        <v>560</v>
+      </c>
+      <c r="E15" t="n">
         <v>580</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>600</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>3.57</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1403,33 +1463,36 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
         <v>62</v>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>8.77</v>
+      <c r="F16" t="n">
+        <v>62</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>8.77</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H16" s="4" t="n">
+        <v>8.77</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1450,33 +1513,36 @@
         <v>143</v>
       </c>
       <c r="D17" t="n">
+        <v>135</v>
+      </c>
+      <c r="E17" t="n">
         <v>122</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>136</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>-4.9</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-14.69</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I17" s="6" t="inlineStr">
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1497,33 +1563,36 @@
         <v>300</v>
       </c>
       <c r="D18" t="n">
+        <v>300</v>
+      </c>
+      <c r="E18" t="n">
         <v>310</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>318</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>3.33</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1544,33 +1613,36 @@
         <v>328</v>
       </c>
       <c r="D19" t="n">
+        <v>328</v>
+      </c>
+      <c r="E19" t="n">
         <v>330</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>338</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>3.05</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>0.61</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1591,33 +1663,36 @@
         <v>1095</v>
       </c>
       <c r="D20" t="n">
+        <v>1175</v>
+      </c>
+      <c r="E20" t="n">
         <v>1025</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1210</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>10.5</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-6.39</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
